--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="120">
   <si>
     <t>Materia</t>
   </si>
@@ -2800,13 +2800,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2815,22 +2815,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,45 +2850,54 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2902,40 +2914,49 @@
         <v>96.7</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>96</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>95</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>93.3</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>96</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>96.7</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>96</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>95</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>93.3</v>
-      </c>
-      <c r="N4">
-        <v>96</v>
-      </c>
-      <c r="O4">
-        <v>96.7</v>
       </c>
       <c r="P4">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>96.7</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -2952,7 +2973,7 @@
         <v>93.3</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -2964,13 +2985,13 @@
         <v>100</v>
       </c>
       <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
         <v>93.3</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
       <c r="L5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -2979,13 +3000,22 @@
         <v>100</v>
       </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
         <v>93.3</v>
       </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3002,40 +3032,49 @@
         <v>100</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>84</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>70</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>73.3</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>88</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>84</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>70</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>73.3</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>88</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3052,40 +3091,49 @@
         <v>80</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>84</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>50</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>63.3</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>56</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>80</v>
       </c>
-      <c r="K7">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>84</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>50</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>63.3</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>56</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>80</v>
       </c>
-      <c r="P7">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3102,40 +3150,49 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
         <v>93.3</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>96</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>93.3</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>96</v>
       </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
-      <c r="P8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3152,7 +3209,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -3170,7 +3227,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3184,8 +3241,17 @@
       <c r="P9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3202,17 +3268,17 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
         <v>96.7</v>
       </c>
-      <c r="I10">
-        <v>100</v>
-      </c>
       <c r="J10">
         <v>100</v>
       </c>
@@ -3220,22 +3286,31 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
         <v>96.7</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
-        <v>100</v>
-      </c>
       <c r="P10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3252,7 +3327,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -3270,7 +3345,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3284,8 +3359,17 @@
       <c r="P11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3302,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -3320,7 +3404,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3334,8 +3418,17 @@
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3352,14 +3445,14 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
         <v>95</v>
       </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
         <v>100</v>
       </c>
@@ -3370,22 +3463,31 @@
         <v>100</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>95</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3402,40 +3504,49 @@
         <v>100</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>96</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
       <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>93.3</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>92</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>96</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>93.3</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>92</v>
       </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -3452,40 +3563,49 @@
         <v>100</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>96</v>
       </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
       <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
         <v>86.7</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>96</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>96</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
         <v>86.7</v>
-      </c>
-      <c r="N15">
-        <v>96</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
       </c>
       <c r="P15">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -3502,17 +3622,17 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>96.7</v>
       </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
       <c r="J16">
         <v>100</v>
       </c>
@@ -3520,22 +3640,31 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>96.7</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -3552,7 +3681,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -3570,7 +3699,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3584,8 +3713,17 @@
       <c r="P17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -3602,7 +3740,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -3620,7 +3758,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -3634,8 +3772,17 @@
       <c r="P18">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3652,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -3670,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -3684,8 +3831,17 @@
       <c r="P19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -3702,17 +3858,17 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
         <v>86.7</v>
       </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
       <c r="J20">
         <v>100</v>
       </c>
@@ -3720,22 +3876,31 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
         <v>86.7</v>
       </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
       <c r="P20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3752,7 +3917,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -3770,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -3784,8 +3949,17 @@
       <c r="P21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -3802,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -3820,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -3834,8 +4008,17 @@
       <c r="P22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3852,40 +4035,49 @@
         <v>93.3</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>84</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>85</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>63.3</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>72</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>93.3</v>
       </c>
-      <c r="K23">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>84</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>85</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>63.3</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>72</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>93.3</v>
       </c>
-      <c r="P23">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3902,7 +4094,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -3920,7 +4112,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -3934,8 +4126,17 @@
       <c r="P24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -3952,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -3970,7 +4171,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -3984,8 +4185,17 @@
       <c r="P25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4002,7 +4212,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -4020,7 +4230,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4034,8 +4244,17 @@
       <c r="P26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4052,7 +4271,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -4070,7 +4289,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4084,8 +4303,17 @@
       <c r="P27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4102,17 +4330,17 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>100</v>
       </c>
       <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
         <v>96.7</v>
       </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
       <c r="J28">
         <v>100</v>
       </c>
@@ -4120,26 +4348,35 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
         <v>96.7</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
       <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -200,184 +200,19 @@
     <t>ABAD</t>
   </si>
   <si>
-    <t>AVELLEIRA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>MARITZA</t>
   </si>
   <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>DEBORA GEORGINA</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>CRISTINA KARELY</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DARLET VICTORIA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
-    <t>JONATHAN MOISES</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>AMIR ALONSO</t>
-  </si>
-  <si>
-    <t>GEMMA MARIA</t>
-  </si>
-  <si>
-    <t>NOEMI</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>PAULA MARIA</t>
   </si>
 </sst>
 </file>
@@ -879,28 +714,28 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -921,19 +756,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -956,28 +791,28 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -998,7 +833,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1007,13 +842,13 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1033,28 +868,28 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1075,7 +910,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1084,10 +919,10 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1110,28 +945,28 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1164,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1187,28 +1022,28 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1241,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1264,28 +1099,28 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1309,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1318,10 +1153,10 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1341,28 +1176,28 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1383,22 +1218,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1418,28 +1253,28 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1463,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1472,7 +1307,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1495,28 +1330,28 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1549,10 +1384,10 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1572,28 +1407,28 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1617,7 +1452,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1626,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1649,28 +1484,28 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1691,7 +1526,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1703,10 +1538,10 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1726,28 +1561,28 @@
         <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1771,16 +1606,16 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1803,28 +1638,28 @@
         <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1848,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1857,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1880,28 +1715,28 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1922,10 +1757,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -1934,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1957,28 +1792,28 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2002,7 +1837,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2011,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2034,28 +1869,28 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2079,16 +1914,16 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2111,28 +1946,28 @@
         <v>7</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2165,7 +2000,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2188,28 +2023,28 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2233,16 +2068,16 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2265,28 +2100,28 @@
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2307,10 +2142,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2319,10 +2154,10 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2342,28 +2177,28 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2396,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2419,28 +2254,28 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2473,10 +2308,10 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2496,28 +2331,28 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2541,16 +2376,16 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2573,28 +2408,28 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2624,10 +2459,10 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2650,28 +2485,28 @@
         <v>7</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2692,10 +2527,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2704,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2727,28 +2562,28 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2772,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2781,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2914,46 +2749,46 @@
         <v>96.7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>96</v>
       </c>
       <c r="H4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J4">
         <v>96</v>
       </c>
       <c r="K4">
+        <v>98.3</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>94</v>
+      </c>
+      <c r="N4">
+        <v>97.5</v>
+      </c>
+      <c r="O4">
         <v>96.7</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>96</v>
-      </c>
-      <c r="N4">
-        <v>95</v>
-      </c>
-      <c r="O4">
-        <v>93.3</v>
       </c>
       <c r="P4">
         <v>96</v>
       </c>
       <c r="Q4">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2973,7 +2808,7 @@
         <v>93.3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -2982,7 +2817,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -2991,7 +2826,7 @@
         <v>93.3</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3000,7 +2835,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3009,7 +2844,7 @@
         <v>93.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3032,46 +2867,46 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>84</v>
       </c>
       <c r="H6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I6">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="J6">
         <v>88</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O6">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="P6">
         <v>88</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3091,16 +2926,16 @@
         <v>80</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>84</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I7">
-        <v>63.3</v>
+        <v>71.7</v>
       </c>
       <c r="J7">
         <v>56</v>
@@ -3109,16 +2944,16 @@
         <v>80</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N7">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="O7">
-        <v>63.3</v>
+        <v>71.7</v>
       </c>
       <c r="P7">
         <v>56</v>
@@ -3127,10 +2962,10 @@
         <v>80</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3150,7 +2985,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -3159,7 +2994,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J8">
         <v>96</v>
@@ -3168,7 +3003,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3177,7 +3012,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P8">
         <v>96</v>
@@ -3186,7 +3021,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3209,7 +3044,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -3218,7 +3053,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3227,16 +3062,16 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3245,10 +3080,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3268,7 +3103,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -3277,7 +3112,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3286,7 +3121,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3295,7 +3130,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3304,7 +3139,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3327,7 +3162,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -3336,7 +3171,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3345,7 +3180,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3354,7 +3189,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3363,7 +3198,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3386,7 +3221,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -3404,7 +3239,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3422,7 +3257,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3445,13 +3280,13 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -3463,13 +3298,13 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3481,10 +3316,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3504,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>96</v>
@@ -3513,37 +3348,37 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>92</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="P14">
         <v>92</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3563,7 +3398,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>96</v>
@@ -3572,7 +3407,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="J15">
         <v>96</v>
@@ -3581,16 +3416,16 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>86.7</v>
+        <v>88.3</v>
       </c>
       <c r="P15">
         <v>96</v>
@@ -3599,10 +3434,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3622,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -3631,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3640,7 +3475,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -3649,7 +3484,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3658,7 +3493,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3681,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -3699,7 +3534,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3717,7 +3552,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3740,7 +3575,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -3758,7 +3593,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -3776,7 +3611,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3799,7 +3634,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -3808,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -3817,7 +3652,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -3826,7 +3661,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -3835,7 +3670,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3858,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -3867,7 +3702,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -3876,16 +3711,16 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -3894,10 +3729,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3917,7 +3752,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -3926,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -3935,7 +3770,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -3944,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3953,7 +3788,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3976,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -3994,7 +3829,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -4012,7 +3847,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4035,43 +3870,43 @@
         <v>93.3</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>84</v>
       </c>
       <c r="H23">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="I23">
-        <v>63.3</v>
+        <v>66.7</v>
       </c>
       <c r="J23">
         <v>72</v>
       </c>
       <c r="K23">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>84</v>
       </c>
       <c r="N23">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O23">
-        <v>63.3</v>
+        <v>66.7</v>
       </c>
       <c r="P23">
         <v>72</v>
       </c>
       <c r="Q23">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
         <v>84</v>
@@ -4094,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -4103,16 +3938,16 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4121,16 +3956,16 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4153,7 +3988,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -4171,7 +4006,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4189,7 +4024,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4212,7 +4047,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -4227,13 +4062,13 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4245,13 +4080,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4271,7 +4106,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -4280,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4289,16 +4124,16 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4307,10 +4142,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4330,7 +4165,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -4339,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4348,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4357,7 +4192,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -4366,7 +4201,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4426,7 +4261,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4435,27 +4270,30 @@
         <v>25</v>
       </c>
       <c r="D2">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>84</v>
+      </c>
+      <c r="G2" s="2">
+        <v>16</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4476,7 +4314,7 @@
         <v>16</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4508,7 +4346,7 @@
         <v>12</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4519,7 +4357,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4528,19 +4366,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4551,7 +4389,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -4572,7 +4410,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4604,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4620,7 +4458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4647,506 +4485,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920332</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920333</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920334</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920335</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920137</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920338</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920339</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920340</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920343</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920341</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920342</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920343</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920344</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920345</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920347</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920348</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920350</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920149</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920351</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920322</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920352</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920353</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920354</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5154,7 +4492,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5192,525 +4530,42 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920333</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920335</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920137</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920336</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920338</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920339</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920340</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920343</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920341</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920342</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920343</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920344</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920345</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920347</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920348</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920350</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920351</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920322</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920352</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920353</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920354</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -179,9 +182,6 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -197,22 +197,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CORONA</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
   </si>
   <si>
     <t>MARITZA</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
+    <t>ANGEL DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -726,13 +735,13 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -803,13 +812,13 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -880,13 +889,13 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -916,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -957,13 +966,13 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1034,13 +1043,13 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1070,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1111,13 +1120,13 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1147,13 +1156,13 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1188,13 +1197,13 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1265,13 +1274,13 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1301,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1342,13 +1351,13 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1378,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1419,13 +1428,13 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1455,13 +1464,13 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1496,13 +1505,13 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1532,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1573,13 +1582,13 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1615,7 +1624,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1650,13 +1659,13 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1727,13 +1736,13 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -1804,13 +1813,13 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -1881,13 +1890,13 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -1917,7 +1926,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -1958,13 +1967,13 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2000,7 +2009,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2035,13 +2044,13 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2112,13 +2121,13 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2189,13 +2198,13 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2266,13 +2275,13 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2308,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2343,13 +2352,13 @@
         <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2385,7 +2394,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2420,13 +2429,13 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2462,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2497,13 +2506,13 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>6</v>
@@ -2533,7 +2542,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2574,13 +2583,13 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2820,7 +2829,7 @@
         <v>98.3</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K5">
         <v>93.3</v>
@@ -2838,7 +2847,7 @@
         <v>98.3</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>93.3</v>
@@ -2879,13 +2888,13 @@
         <v>76.7</v>
       </c>
       <c r="J6">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K6">
         <v>90</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>76</v>
@@ -2897,13 +2906,13 @@
         <v>76.7</v>
       </c>
       <c r="P6">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q6">
         <v>90</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S6">
         <v>76</v>
@@ -2938,13 +2947,13 @@
         <v>71.7</v>
       </c>
       <c r="J7">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="K7">
         <v>80</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M7">
         <v>92</v>
@@ -2956,13 +2965,13 @@
         <v>71.7</v>
       </c>
       <c r="P7">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="Q7">
         <v>80</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S7">
         <v>92</v>
@@ -2997,7 +3006,7 @@
         <v>96.7</v>
       </c>
       <c r="J8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3015,7 +3024,7 @@
         <v>96.7</v>
       </c>
       <c r="P8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3351,7 +3360,7 @@
         <v>95</v>
       </c>
       <c r="J14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K14">
         <v>95</v>
@@ -3369,7 +3378,7 @@
         <v>95</v>
       </c>
       <c r="P14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q14">
         <v>95</v>
@@ -3882,13 +3891,13 @@
         <v>66.7</v>
       </c>
       <c r="J23">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K23">
         <v>86.7</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M23">
         <v>84</v>
@@ -3900,13 +3909,13 @@
         <v>66.7</v>
       </c>
       <c r="P23">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="Q23">
         <v>86.7</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S23">
         <v>84</v>
@@ -3941,7 +3950,7 @@
         <v>98.3</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K24">
         <v>96.7</v>
@@ -3959,7 +3968,7 @@
         <v>98.3</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q24">
         <v>96.7</v>
@@ -4118,7 +4127,7 @@
         <v>98.3</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4136,7 +4145,7 @@
         <v>98.3</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4261,7 +4270,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4270,19 +4279,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4293,7 +4302,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4314,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4325,7 +4334,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4334,19 +4343,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4357,7 +4366,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4378,7 +4387,7 @@
         <v>12</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4389,7 +4398,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -4398,19 +4407,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4492,7 +4501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4524,22 +4533,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4550,21 +4559,67 @@
         <v>21330051920353</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920331</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920347</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
         <v>64</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3">
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -167,24 +167,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,31 +197,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
   </si>
 </sst>
 </file>
@@ -747,22 +738,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -780,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -824,28 +815,28 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -854,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -901,25 +892,25 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -978,22 +969,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1002,16 +993,16 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1055,25 +1046,25 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1082,10 +1073,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1132,40 +1123,40 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1209,22 +1200,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1236,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1286,22 +1277,22 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1363,22 +1354,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1393,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1440,34 +1431,34 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1517,31 +1508,31 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1594,28 +1585,28 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1671,22 +1662,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1748,25 +1739,25 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1825,34 +1816,34 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1902,22 +1893,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1929,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1979,25 +1970,25 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2009,7 +2000,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2056,22 +2047,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2086,7 +2077,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2133,28 +2124,28 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2166,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2213,19 +2204,19 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2234,16 +2225,16 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2287,22 +2278,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2364,28 +2355,28 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2441,22 +2432,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2518,40 +2509,40 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2595,22 +2586,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2782,22 +2773,22 @@
         <v>94</v>
       </c>
       <c r="N4">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="O4">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="P4">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q4">
-        <v>98.3</v>
+        <v>61.5</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>94</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2844,13 +2835,13 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P5">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -2900,22 +2891,22 @@
         <v>76</v>
       </c>
       <c r="N6">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="O6">
-        <v>76.7</v>
+        <v>47.9</v>
       </c>
       <c r="P6">
-        <v>92</v>
+        <v>62.2</v>
       </c>
       <c r="Q6">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>63.3</v>
       </c>
       <c r="S6">
-        <v>76</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2959,22 +2950,22 @@
         <v>92</v>
       </c>
       <c r="N7">
-        <v>65</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O7">
-        <v>71.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="P7">
-        <v>76</v>
+        <v>83.8</v>
       </c>
       <c r="Q7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="R7">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="S7">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3021,10 +3012,10 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P8">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3080,7 +3071,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3092,7 +3083,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3139,7 +3130,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3198,7 +3189,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3313,10 +3304,10 @@
         <v>96</v>
       </c>
       <c r="N13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3328,7 +3319,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3372,22 +3363,22 @@
         <v>92</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="P14">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>92</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3434,10 +3425,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>88.3</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3446,7 +3437,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3493,7 +3484,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3505,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3670,7 +3661,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -3729,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -3741,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3788,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3844,10 +3835,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -3903,22 +3894,22 @@
         <v>84</v>
       </c>
       <c r="N23">
-        <v>92.5</v>
+        <v>57.8</v>
       </c>
       <c r="O23">
-        <v>66.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="P23">
-        <v>84</v>
+        <v>89.2</v>
       </c>
       <c r="Q23">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R23">
+        <v>93.3</v>
+      </c>
+      <c r="S23">
         <v>90</v>
-      </c>
-      <c r="S23">
-        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3965,13 +3956,13 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P24">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4024,7 +4015,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4083,19 +4074,19 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>94</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4139,22 +4130,22 @@
         <v>92</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="O27">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P27">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>92</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4201,7 +4192,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -4270,7 +4261,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4279,19 +4270,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4302,7 +4293,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4311,19 +4302,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4334,7 +4325,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4343,16 +4334,16 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>96</v>
+      </c>
+      <c r="G4" s="2">
         <v>4</v>
-      </c>
-      <c r="F4" s="2">
-        <v>84</v>
-      </c>
-      <c r="G4" s="2">
-        <v>16</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -4366,7 +4357,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4375,19 +4366,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4398,7 +4389,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -4407,19 +4398,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4430,7 +4421,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -4451,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4501,7 +4492,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4533,22 +4524,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920353</v>
+        <v>21330051920334</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4556,19 +4547,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920353</v>
+        <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>49</v>
@@ -4579,47 +4570,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920331</v>
+        <v>21330051920149</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920347</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -747,7 +747,7 @@
         <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -2782,7 +2782,7 @@
         <v>97.3</v>
       </c>
       <c r="Q4">
-        <v>61.5</v>
+        <v>92.7</v>
       </c>
       <c r="R4">
         <v>100</v>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -2201,7 +2201,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2219,7 +2219,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -3894,7 +3894,7 @@
         <v>84</v>
       </c>
       <c r="N23">
-        <v>57.8</v>
+        <v>79.7</v>
       </c>
       <c r="O23">
         <v>77.09999999999999</v>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4282,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4302,19 +4302,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G3" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4492,7 +4492,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4539,7 +4539,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4562,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4582,12 +4582,35 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>49</v>
       </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -756,22 +756,22 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -833,22 +833,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -993,16 +993,16 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,22 +1064,22 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,22 +1141,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1218,22 +1218,22 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1295,22 +1295,22 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1375,19 +1375,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1452,19 +1452,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1526,22 +1526,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1603,22 +1603,22 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1683,19 +1683,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1757,22 +1757,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1837,16 +1837,16 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -1914,19 +1914,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1988,22 +1988,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,22 +2065,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2142,22 +2142,22 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2225,16 +2225,16 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2376,13 +2376,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2459,10 +2459,10 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2527,22 +2527,22 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2607,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -4282,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4442,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5APM - Estadisticos 20231.xlsx
+++ b/grupos/5APM - Estadisticos 20231.xlsx
@@ -756,22 +756,22 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -833,22 +833,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -993,16 +993,16 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,22 +1064,22 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,22 +1141,22 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1218,22 +1218,22 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1295,22 +1295,22 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1375,19 +1375,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1452,19 +1452,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1526,22 +1526,22 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1603,22 +1603,22 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1683,19 +1683,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1757,22 +1757,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1837,16 +1837,16 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -1914,19 +1914,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1988,22 +1988,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,22 +2065,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2142,22 +2142,22 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2225,16 +2225,16 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2376,13 +2376,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2459,10 +2459,10 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2527,22 +2527,22 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2607,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -4282,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4378,7 +4378,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4442,7 +4442,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
